--- a/output/reports/cv_experiment_Ridge_qcut_regression.xlsx
+++ b/output/reports/cv_experiment_Ridge_qcut_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3199372291564941</v>
+        <v>0.1782455444335938</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.9095295397201048</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.9134071819812636</v>
       </c>
       <c r="G2" t="n">
-        <v>5.815874837237964e-12</v>
+        <v>5.798959174155399</v>
       </c>
       <c r="H2" t="n">
-        <v>4.546447319119009e-12</v>
+        <v>4.192639414719826</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'auto', 'alpha': 1e-05}</t>
+          <t>{'solver': 'svd', 'alpha': 1e-05}</t>
         </is>
       </c>
     </row>
@@ -526,91 +526,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.328242301940918</v>
+        <v>0.2461557388305664</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0.9087497339209655</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0.9134071819812641</v>
       </c>
       <c r="G3" t="n">
-        <v>5.815874837237964e-12</v>
+        <v>5.79895917415538</v>
       </c>
       <c r="H3" t="n">
-        <v>4.546447319119009e-12</v>
+        <v>4.192639414719824</v>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>{'solver': 'auto', 'alpha': 1e-05}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.5251638889312744</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>5.815874837237964e-12</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4.546447319119009e-12</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'solver': 'auto', 'alpha': 1e-05}</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.7051148414611816</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>5.815874837237964e-12</v>
-      </c>
-      <c r="H5" t="n">
-        <v>4.546447319119009e-12</v>
-      </c>
-      <c r="I5" t="inlineStr">
         <is>
           <t>{'solver': 'auto', 'alpha': 1e-05}</t>
         </is>
@@ -627,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -692,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3199372291564941</v>
+        <v>0.1782455444335938</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.9095295397201048</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.9134071819812636</v>
       </c>
       <c r="G2" t="n">
-        <v>5.815874837237964e-12</v>
+        <v>5.798959174155399</v>
       </c>
       <c r="H2" t="n">
-        <v>4.546447319119009e-12</v>
+        <v>4.192639414719826</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'auto', 'alpha': 1e-05}</t>
+          <t>{'solver': 'svd', 'alpha': 1e-05}</t>
         </is>
       </c>
     </row>
@@ -727,91 +657,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.328242301940918</v>
+        <v>0.2461557388305664</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0.9087497339209655</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0.9134071819812641</v>
       </c>
       <c r="G3" t="n">
-        <v>5.815874837237964e-12</v>
+        <v>5.79895917415538</v>
       </c>
       <c r="H3" t="n">
-        <v>4.546447319119009e-12</v>
+        <v>4.192639414719824</v>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>{'solver': 'auto', 'alpha': 1e-05}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.5251638889312744</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>5.815874837237964e-12</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4.546447319119009e-12</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'solver': 'auto', 'alpha': 1e-05}</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.7051148414611816</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>5.815874837237964e-12</v>
-      </c>
-      <c r="H5" t="n">
-        <v>4.546447319119009e-12</v>
-      </c>
-      <c r="I5" t="inlineStr">
         <is>
           <t>{'solver': 'auto', 'alpha': 1e-05}</t>
         </is>
